--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_ending5(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_ending5(3).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_结局5（下）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="299">
   <si>
     <t>ID</t>
   </si>
@@ -90,9 +90,15 @@
     <t>black</t>
   </si>
   <si>
+    <t>6 enhanced oceanframemusic-horror-background-music</t>
+  </si>
+  <si>
     <t>false</t>
   </si>
   <si>
+    <t>unlockmusic(Music6)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=0</t>
   </si>
   <si>
@@ -121,6 +127,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>你曾试图调阅过</t>
     </r>
     <r>
@@ -266,6 +277,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>通缉对象是大卫</t>
     </r>
     <r>
@@ -371,6 +387,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>直到某天，你在训练场上看见一个新兵。他的眼神。那种空洞又熟悉的眼神。和你三个月前盖曼在昏迷前看向你们的眼神一模一样</t>
     </r>
     <r>
@@ -458,6 +479,9 @@
   </si>
   <si>
     <t>达成结局：【梦之渊】</t>
+  </si>
+  <si>
+    <t>unlockending(Ending3)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=31</t>
@@ -2244,7 +2268,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" ht="60" spans="1:12">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2270,21 +2294,21 @@
         <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" ht="54" spans="1:12">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -2302,7 +2326,7 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -2314,15 +2338,15 @@
         <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" ht="55.5" spans="1:12">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2340,7 +2364,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -2355,12 +2379,12 @@
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" ht="28.5" spans="1:12">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2378,7 +2402,7 @@
         <v>15</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -2393,12 +2417,12 @@
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" ht="42" spans="1:12">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2416,7 +2440,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -2431,12 +2455,12 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" ht="58.5" spans="1:12">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2454,7 +2478,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -2469,12 +2493,12 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" ht="42" spans="1:12">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -2492,7 +2516,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -2507,12 +2531,12 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:12">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -2530,7 +2554,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -2545,12 +2569,12 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" ht="55.5" spans="1:12">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -2568,7 +2592,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -2583,12 +2607,12 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" ht="27" spans="1:12">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -2606,7 +2630,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -2621,12 +2645,12 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" ht="40.5" spans="1:12">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -2644,7 +2668,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -2659,12 +2683,12 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -2682,7 +2706,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -2697,12 +2721,12 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" ht="43.5" spans="1:12">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -2720,7 +2744,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -2735,12 +2759,12 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" ht="40.5" spans="1:12">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -2758,7 +2782,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -2773,12 +2797,12 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" ht="40.5" spans="1:12">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -2796,7 +2820,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -2808,15 +2832,15 @@
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" ht="55.5" spans="1:12">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -2834,7 +2858,7 @@
         <v>15</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -2849,12 +2873,12 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -2872,7 +2896,7 @@
         <v>15</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -2887,12 +2911,12 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" ht="67.5" spans="1:12">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -2910,7 +2934,7 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
@@ -2925,12 +2949,12 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" ht="67.5" spans="1:12">
       <c r="A20" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -2948,7 +2972,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -2963,12 +2987,12 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" ht="27" spans="1:12">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -2986,7 +3010,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -2998,15 +3022,15 @@
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" ht="40.5" spans="1:12">
       <c r="A22" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3024,7 +3048,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3039,12 +3063,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" ht="55.5" spans="1:12">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3062,7 +3086,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3077,12 +3101,12 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" ht="40.5" spans="1:12">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3100,7 +3124,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3112,15 +3136,15 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" ht="40.5" spans="1:12">
       <c r="A25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3138,7 +3162,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3153,12 +3177,12 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" ht="55.5" spans="1:12">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3176,7 +3200,7 @@
         <v>15</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3188,15 +3212,15 @@
         <v>15</v>
       </c>
       <c r="K26" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L26" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" ht="73.5" spans="1:12">
       <c r="A27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3214,7 +3238,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3229,12 +3253,12 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3252,7 +3276,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
@@ -3267,12 +3291,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" ht="58.5" spans="1:12">
       <c r="A29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3290,7 +3314,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3302,15 +3326,15 @@
         <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L29" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" ht="28.5" spans="1:12">
       <c r="A30" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3328,7 +3352,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3343,12 +3367,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3366,7 +3390,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3381,12 +3405,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3404,7 +3428,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3419,12 +3443,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3441,8 +3465,8 @@
       <c r="F33" t="s">
         <v>15</v>
       </c>
-      <c r="G33" t="s">
-        <v>117</v>
+      <c r="G33" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3454,10 +3478,10 @@
         <v>15</v>
       </c>
       <c r="K33" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="L33" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -3478,122 +3502,122 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B12" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B13" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" ht="105" spans="1:2">
       <c r="A14" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B15" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -3615,616 +3639,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="F3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B5" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D6" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E6" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F6" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C7" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F7" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C8" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D8" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E8" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F8" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C9" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D9" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E9" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F9" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C10" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E10" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F10" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B11" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C11" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E11" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F11" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B12" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C12" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D12" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E12" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F12" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C13" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D13" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E13" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B14" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C14" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D14" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E14" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F14" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C15" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E15" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F15" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C16" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D16" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E16" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F16" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C17" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="D17" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E17" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F17" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C18" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D18" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E18" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F18" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B19" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C19" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D19" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E19" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F19" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B20" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C20" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D20" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E20" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="F20" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B21" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C21" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D21" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E21" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="F21" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B22" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C22" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D22" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E22" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F22" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B23" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C23" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D23" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E23" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F23" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B24" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D24" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E24" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F24" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C25" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D25" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E25" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="F25" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B26" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C26" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D26" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E26" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F26" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B27" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C27" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D27" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E27" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F27" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s">
+        <v>281</v>
+      </c>
+      <c r="C28" t="s">
+        <v>282</v>
+      </c>
+      <c r="D28" t="s">
         <v>278</v>
       </c>
-      <c r="C28" t="s">
-        <v>279</v>
-      </c>
-      <c r="D28" t="s">
-        <v>275</v>
-      </c>
       <c r="E28" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F28" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B29" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C29" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D29" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E29" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F29" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C30" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E30" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F30" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D31" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
